--- a/scenarios/02_mike_detector_engineer/2.5_well_capacity_optimization/outputs/well_capacity_results.xlsx
+++ b/scenarios/02_mike_detector_engineer/2.5_well_capacity_optimization/outputs/well_capacity_results.xlsx
@@ -2352,31 +2352,31 @@
         <v>0.11</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>8.869999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>17.43</v>
+        <v>17.95</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>56.16</v>
+        <v>56.96</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>114.87</v>
+        <v>115.52</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>278.3</v>
+        <v>278.64</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>738.24</v>
+        <v>738.38</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1413.33</v>
+        <v>1413.4</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>1413.33</v>
+        <v>1413.4</v>
       </c>
     </row>
     <row r="5">
@@ -2384,34 +2384,34 @@
         <v>0.001247</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2.93</v>
+        <v>3.07</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>10.57</v>
+        <v>11</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>20.53</v>
+        <v>21.22</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>64.31999999999999</v>
+        <v>65.28</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>129.59</v>
+        <v>130.34</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>311.47</v>
+        <v>311.85</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>824.6900000000001</v>
+        <v>824.84</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1413.27</v>
+        <v>1413.36</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1413.27</v>
+        <v>1413.36</v>
       </c>
     </row>
     <row r="6">
@@ -2419,34 +2419,34 @@
         <v>0.001555</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>12.51</v>
+        <v>13.08</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>24.04</v>
+        <v>24.93</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>73.37</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>145.92</v>
+        <v>146.78</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>348.44</v>
+        <v>348.87</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>921.2</v>
+        <v>921.36</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1413.2</v>
+        <v>1413.31</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>1413.2</v>
+        <v>1413.31</v>
       </c>
     </row>
     <row r="7">
@@ -2454,34 +2454,34 @@
         <v>0.00194</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4.16</v>
+        <v>4.42</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>14.71</v>
+        <v>15.47</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>27.99</v>
+        <v>29.12</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>83.39</v>
+        <v>84.73</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>164.05</v>
+        <v>165.04</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>389.66</v>
+        <v>390.14</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1028.94</v>
+        <v>1029.13</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1413.1</v>
+        <v>1413.24</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1413.1</v>
+        <v>1413.24</v>
       </c>
     </row>
     <row r="8">
@@ -2489,34 +2489,34 @@
         <v>0.002419</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>4.91</v>
+        <v>5.26</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>17.2</v>
+        <v>18.18</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>32.41</v>
+        <v>33.82</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>94.48999999999999</v>
+        <v>96.06</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>184.21</v>
+        <v>185.33</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>435.64</v>
+        <v>436.18</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1149.25</v>
+        <v>1149.46</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1412.99</v>
+        <v>1413.16</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>1412.99</v>
+        <v>1413.16</v>
       </c>
     </row>
     <row r="9">
@@ -2524,34 +2524,34 @@
         <v>0.003016</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>5.76</v>
+        <v>6.23</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>20</v>
+        <v>21.24</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>37.33</v>
+        <v>39.06</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>106.8</v>
+        <v>108.62</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>206.63</v>
+        <v>207.89</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>486.93</v>
+        <v>487.54</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1283.57</v>
+        <v>1283.81</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1412.84</v>
+        <v>1413.06</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>1412.84</v>
+        <v>1413.06</v>
       </c>
     </row>
     <row r="10">
@@ -2559,34 +2559,34 @@
         <v>0.003762</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>6.73</v>
+        <v>7.32</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>23.12</v>
+        <v>24.68</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>42.79</v>
+        <v>44.9</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>120.45</v>
+        <v>122.54</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>231.57</v>
+        <v>233</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>544.17</v>
+        <v>544.85</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1412.66</v>
+        <v>1412.93</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1412.66</v>
+        <v>1412.93</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1412.66</v>
+        <v>1412.93</v>
       </c>
     </row>
     <row r="11">
@@ -2594,34 +2594,34 @@
         <v>0.004691</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>7.81</v>
+        <v>8.56</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>26.6</v>
+        <v>28.51</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>48.86</v>
+        <v>51.38</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>135.6</v>
+        <v>137.99</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>259.36</v>
+        <v>260.96</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>608.05</v>
+        <v>608.8099999999999</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1412.44</v>
+        <v>1412.77</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1412.44</v>
+        <v>1412.77</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1412.44</v>
+        <v>1412.77</v>
       </c>
     </row>
     <row r="12">
@@ -2629,34 +2629,34 @@
         <v>0.00585</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>9.01</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>30.46</v>
+        <v>32.77</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>55.58</v>
+        <v>58.56</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>152.42</v>
+        <v>155.15</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>290.31</v>
+        <v>292.12</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>679.35</v>
+        <v>680.2</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1412.16</v>
+        <v>1412.58</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1412.16</v>
+        <v>1412.58</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>1412.16</v>
+        <v>1412.58</v>
       </c>
     </row>
     <row r="13">
@@ -2664,34 +2664,34 @@
         <v>0.007296</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>10.35</v>
+        <v>11.5</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>34.74</v>
+        <v>37.51</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>63.02</v>
+        <v>66.52</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>171.12</v>
+        <v>174.22</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>324.8</v>
+        <v>326.84</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>758.9400000000001</v>
+        <v>759.89</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1411.81</v>
+        <v>1412.33</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1411.81</v>
+        <v>1412.33</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>1411.81</v>
+        <v>1412.33</v>
       </c>
     </row>
     <row r="14">
@@ -2699,34 +2699,34 @@
         <v>0.009098999999999999</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>11.83</v>
+        <v>13.23</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>39.48</v>
+        <v>42.76</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>71.27</v>
+        <v>75.34</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>191.92</v>
+        <v>195.42</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>363.27</v>
+        <v>365.55</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>847.79</v>
+        <v>848.85</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1411.38</v>
+        <v>1412.02</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1411.38</v>
+        <v>1412.02</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>1411.38</v>
+        <v>1412.02</v>
       </c>
     </row>
     <row r="15">
@@ -2734,34 +2734,34 @@
         <v>0.011347</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>0.63</v>
+        <v>0.72</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>13.48</v>
+        <v>15.15</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>44.74</v>
+        <v>48.58</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>80.42</v>
+        <v>85.11</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>215.07</v>
+        <v>219.03</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>406.17</v>
+        <v>408.72</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>946.98</v>
+        <v>948.17</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1410.83</v>
+        <v>1411.64</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1410.83</v>
+        <v>1411.64</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>1410.83</v>
+        <v>1411.64</v>
       </c>
     </row>
     <row r="16">
@@ -2769,34 +2769,34 @@
         <v>0.01415</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.72</v>
+        <v>0.83</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>15.3</v>
+        <v>17.27</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>50.57</v>
+        <v>55.02</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>90.56999999999999</v>
+        <v>95.95999999999999</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>240.85</v>
+        <v>245.31</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>454.02</v>
+        <v>456.88</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1057.73</v>
+        <v>1059.06</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1410.16</v>
+        <v>1411.16</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1410.16</v>
+        <v>1411.16</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1410.16</v>
+        <v>1411.16</v>
       </c>
     </row>
     <row r="17">
@@ -2804,34 +2804,34 @@
         <v>0.017647</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>17.33</v>
+        <v>19.63</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>57.03</v>
+        <v>62.17</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>101.84</v>
+        <v>107.99</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>269.58</v>
+        <v>274.58</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>507.42</v>
+        <v>510.62</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>1181.39</v>
+        <v>1182.87</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1409.32</v>
+        <v>1410.57</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1409.32</v>
+        <v>1410.57</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1409.32</v>
+        <v>1410.57</v>
       </c>
     </row>
     <row r="18">
@@ -2839,34 +2839,34 @@
         <v>0.022007</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>19.57</v>
+        <v>22.24</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>64.2</v>
+        <v>70.09</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>114.37</v>
+        <v>121.36</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>301.59</v>
+        <v>307.22</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>567.01</v>
+        <v>570.59</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>1319.46</v>
+        <v>1321.12</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>1408.27</v>
+        <v>1409.83</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>1408.27</v>
+        <v>1409.83</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>1408.27</v>
+        <v>1409.83</v>
       </c>
     </row>
     <row r="19">
@@ -2874,34 +2874,34 @@
         <v>0.027445</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>22.05</v>
+        <v>25.14</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>72.17</v>
+        <v>78.89</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>128.3</v>
+        <v>136.22</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>337.29</v>
+        <v>343.6</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>633.51</v>
+        <v>637.52</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>1406.97</v>
+        <v>1408.9</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1406.97</v>
+        <v>1408.9</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>1406.97</v>
+        <v>1408.9</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>1406.97</v>
+        <v>1408.9</v>
       </c>
     </row>
     <row r="20">
@@ -2909,34 +2909,34 @@
         <v>0.034226</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>24.81</v>
+        <v>28.35</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>81.02</v>
+        <v>88.66</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>143.8</v>
+        <v>152.75</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>377.11</v>
+        <v>384.18</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>707.75</v>
+        <v>712.23</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1405.35</v>
+        <v>1407.76</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1405.35</v>
+        <v>1407.76</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1405.35</v>
+        <v>1407.76</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1405.35</v>
+        <v>1407.76</v>
       </c>
     </row>
     <row r="21">
@@ -2944,34 +2944,34 @@
         <v>0.042683</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>27.88</v>
+        <v>31.91</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>90.87</v>
+        <v>99.52</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>161.06</v>
+        <v>171.15</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>421.53</v>
+        <v>429.45</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>790.62</v>
+        <v>795.64</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1403.35</v>
+        <v>1406.33</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1403.35</v>
+        <v>1406.33</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1403.35</v>
+        <v>1406.33</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>1403.35</v>
+        <v>1406.33</v>
       </c>
     </row>
     <row r="22">
@@ -2979,34 +2979,34 @@
         <v>0.053229</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>31.29</v>
+        <v>35.86</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>101.83</v>
+        <v>111.6</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>180.29</v>
+        <v>191.64</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>471.09</v>
+        <v>479.95</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>883.15</v>
+        <v>888.75</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1400.85</v>
+        <v>1404.56</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>1400.85</v>
+        <v>1404.56</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1400.85</v>
+        <v>1404.56</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>1400.85</v>
+        <v>1404.56</v>
       </c>
     </row>
     <row r="23">
@@ -3014,34 +3014,34 @@
         <v>0.066382</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.66</v>
+        <v>1.96</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>35.08</v>
+        <v>40.26</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>114.03</v>
+        <v>125.05</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>201.73</v>
+        <v>214.48</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>526.4</v>
+        <v>536.3200000000001</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>986.4400000000001</v>
+        <v>992.7</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1397.76</v>
+        <v>1402.36</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1397.76</v>
+        <v>1402.36</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1397.76</v>
+        <v>1402.36</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>1397.76</v>
+        <v>1402.36</v>
       </c>
     </row>
     <row r="24">
@@ -3049,34 +3049,34 @@
         <v>0.082784</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>39.3</v>
+        <v>45.15</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>127.63</v>
+        <v>140.03</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>225.62</v>
+        <v>239.94</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>588.14</v>
+        <v>599.23</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1101.78</v>
+        <v>1108.77</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>1393.94</v>
+        <v>1399.63</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>1393.94</v>
+        <v>1399.63</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>1393.94</v>
+        <v>1399.63</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1393.94</v>
+        <v>1399.63</v>
       </c>
     </row>
     <row r="25">
@@ -3084,34 +3084,34 @@
         <v>0.103239</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>2.09</v>
+        <v>2.47</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>44.01</v>
+        <v>50.6</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>142.79</v>
+        <v>156.72</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>252.27</v>
+        <v>268.32</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>657.05</v>
+        <v>669.45</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1230.55</v>
+        <v>1238.37</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>1389.21</v>
+        <v>1396.24</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1389.21</v>
+        <v>1396.24</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>1389.21</v>
+        <v>1396.24</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>1389.21</v>
+        <v>1396.24</v>
       </c>
     </row>
     <row r="26">
@@ -3119,34 +3119,34 @@
         <v>0.128748</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>2.34</v>
+        <v>2.77</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>49.25</v>
+        <v>56.66</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>159.69</v>
+        <v>175.32</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>282</v>
+        <v>299.98</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>733.98</v>
+        <v>747.84</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>1374.35</v>
+        <v>1383.08</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>1383.38</v>
+        <v>1392.06</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>1383.38</v>
+        <v>1392.06</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>1383.38</v>
+        <v>1392.06</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>1383.38</v>
+        <v>1392.06</v>
       </c>
     </row>
     <row r="27">
@@ -3154,34 +3154,34 @@
         <v>0.160561</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>55.09</v>
+        <v>63.42</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>178.54</v>
+        <v>196.06</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>315.17</v>
+        <v>335.3</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>819.87</v>
+        <v>835.36</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1376.21</v>
+        <v>1386.89</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1376.21</v>
+        <v>1386.89</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1376.21</v>
+        <v>1386.89</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1376.21</v>
+        <v>1386.89</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1376.21</v>
+        <v>1386.89</v>
       </c>
     </row>
     <row r="28">
@@ -3189,34 +3189,34 @@
         <v>0.200233</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>2.93</v>
+        <v>3.47</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>61.6</v>
+        <v>70.95</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>199.57</v>
+        <v>219.2</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>352.19</v>
+        <v>374.72</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>915.76</v>
+        <v>933.0700000000001</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1367.43</v>
+        <v>1380.53</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>1367.43</v>
+        <v>1380.53</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1367.43</v>
+        <v>1380.53</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1367.43</v>
+        <v>1380.53</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>1367.43</v>
+        <v>1380.53</v>
       </c>
     </row>
     <row r="29">
@@ -3224,34 +3224,34 @@
         <v>0.249709</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>3.27</v>
+        <v>3.88</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>68.87</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>223.03</v>
+        <v>245.01</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>393.51</v>
+        <v>418.7</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1022.82</v>
+        <v>1042.16</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1356.7</v>
+        <v>1372.71</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1356.7</v>
+        <v>1372.71</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1356.7</v>
+        <v>1372.71</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1356.7</v>
+        <v>1372.71</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1356.7</v>
+        <v>1372.71</v>
       </c>
     </row>
     <row r="30">
@@ -3259,34 +3259,34 @@
         <v>0.311409</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>3.66</v>
+        <v>4.34</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>76.97</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>249.22</v>
+        <v>273.81</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>439.63</v>
+        <v>467.8</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1142.37</v>
+        <v>1163.97</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1343.68</v>
+        <v>1363.15</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>1343.68</v>
+        <v>1363.15</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>1343.68</v>
+        <v>1363.15</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1343.68</v>
+        <v>1363.15</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>1343.68</v>
+        <v>1363.15</v>
       </c>
     </row>
     <row r="31">
@@ -3294,34 +3294,34 @@
         <v>0.388355</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>4.09</v>
+        <v>4.85</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>86.02</v>
+        <v>99.16</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>278.45</v>
+        <v>305.95</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>491.11</v>
+        <v>522.6</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1275.85</v>
+        <v>1299.99</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>1327.95</v>
+        <v>1351.5</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>1327.95</v>
+        <v>1351.5</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1327.95</v>
+        <v>1351.5</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1327.95</v>
+        <v>1351.5</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>1327.95</v>
+        <v>1351.5</v>
       </c>
     </row>
     <row r="32">
@@ -3329,34 +3329,34 @@
         <v>0.484313</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>4.57</v>
+        <v>5.42</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>96.12</v>
+        <v>110.82</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>311.07</v>
+        <v>341.83</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>548.58</v>
+        <v>583.78</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>1309.08</v>
+        <v>1337.38</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1309.08</v>
+        <v>1337.38</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>1309.08</v>
+        <v>1337.38</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1309.08</v>
+        <v>1337.38</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1309.08</v>
+        <v>1337.38</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>1309.08</v>
+        <v>1337.38</v>
       </c>
     </row>
     <row r="33">
@@ -3364,34 +3364,34 @@
         <v>0.603981</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>5.11</v>
+        <v>6.06</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>107.38</v>
+        <v>123.83</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>347.5</v>
+        <v>381.88</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>612.75</v>
+        <v>652.09</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1286.65</v>
+        <v>1320.38</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1286.65</v>
+        <v>1320.38</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>1286.65</v>
+        <v>1320.38</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1286.65</v>
+        <v>1320.38</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>1286.65</v>
+        <v>1320.38</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>1286.65</v>
+        <v>1320.38</v>
       </c>
     </row>
     <row r="34">
@@ -3399,34 +3399,34 @@
         <v>0.7532180000000001</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>5.7</v>
+        <v>6.77</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>119.96</v>
+        <v>138.35</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>388.16</v>
+        <v>426.58</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>684.39</v>
+        <v>728.35</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1260.22</v>
+        <v>1300.06</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>1260.22</v>
+        <v>1300.06</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>1260.22</v>
+        <v>1300.06</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>1260.22</v>
+        <v>1300.06</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>1260.22</v>
+        <v>1300.06</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>1260.22</v>
+        <v>1300.06</v>
       </c>
     </row>
     <row r="35">
@@ -3434,34 +3434,34 @@
         <v>0.939329</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>6.37</v>
+        <v>7.57</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>134</v>
+        <v>154.56</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>433.55</v>
+        <v>476.49</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>764.39</v>
+        <v>813.5</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>1229.43</v>
+        <v>1275.98</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1229.43</v>
+        <v>1275.98</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>1229.43</v>
+        <v>1275.98</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1229.43</v>
+        <v>1275.98</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>1229.43</v>
+        <v>1275.98</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>1229.43</v>
+        <v>1275.98</v>
       </c>
     </row>
     <row r="36">
@@ -3469,34 +3469,34 @@
         <v>1.171427</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>7.12</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>149.68</v>
+        <v>172.66</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>484.24</v>
+        <v>532.22</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>853.71</v>
+        <v>908.5700000000001</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1194.03</v>
+        <v>1247.75</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1194.03</v>
+        <v>1247.75</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>1194.03</v>
+        <v>1247.75</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>1194.03</v>
+        <v>1247.75</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1194.03</v>
+        <v>1247.75</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>1194.03</v>
+        <v>1247.75</v>
       </c>
     </row>
     <row r="37">
@@ -3504,34 +3504,34 @@
         <v>1.460873</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>7.95</v>
+        <v>9.44</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>167.19</v>
+        <v>192.86</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>540.84</v>
+        <v>594.4400000000001</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>953.45</v>
+        <v>1014.73</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1153.89</v>
+        <v>1215.04</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>1153.89</v>
+        <v>1215.04</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>1153.89</v>
+        <v>1215.04</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1153.89</v>
+        <v>1215.04</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>1153.89</v>
+        <v>1215.04</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>1153.89</v>
+        <v>1215.04</v>
       </c>
     </row>
     <row r="38">
@@ -3539,34 +3539,34 @@
         <v>1.821838</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>8.880000000000001</v>
+        <v>10.55</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>186.73</v>
+        <v>215.41</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>604.04</v>
+        <v>663.92</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>1064.82</v>
+        <v>1133.27</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>1109.07</v>
+        <v>1177.64</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>1109.07</v>
+        <v>1177.64</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>1109.07</v>
+        <v>1177.64</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>1109.07</v>
+        <v>1177.64</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>1109.07</v>
+        <v>1177.64</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>1109.07</v>
+        <v>1177.64</v>
       </c>
     </row>
     <row r="39">
@@ -3574,34 +3574,34 @@
         <v>2.271994</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>9.92</v>
+        <v>11.78</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>208.55</v>
+        <v>240.6</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>674.6</v>
+        <v>741.49</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1059.88</v>
+        <v>1135.5</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1059.88</v>
+        <v>1135.5</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>1059.88</v>
+        <v>1135.5</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>1059.88</v>
+        <v>1135.5</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1059.88</v>
+        <v>1135.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>1059.88</v>
+        <v>1135.5</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>1059.88</v>
+        <v>1135.5</v>
       </c>
     </row>
     <row r="40">
@@ -3609,34 +3609,34 @@
         <v>2.833378</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>11.08</v>
+        <v>13.16</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>232.92</v>
+        <v>268.72</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>753.4</v>
+        <v>828.11</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>1006.82</v>
+        <v>1088.78</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>1006.82</v>
+        <v>1088.78</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1006.82</v>
+        <v>1088.78</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>1006.82</v>
+        <v>1088.78</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>1006.82</v>
+        <v>1088.78</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>1006.82</v>
+        <v>1088.78</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>1006.82</v>
+        <v>1088.78</v>
       </c>
     </row>
     <row r="41">
@@ -3644,34 +3644,34 @@
         <v>3.533474</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>12.37</v>
+        <v>14.7</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>260.13</v>
+        <v>300.12</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>841.39</v>
+        <v>924.84</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>950.61</v>
+        <v>1037.88</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>950.61</v>
+        <v>1037.88</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>950.61</v>
+        <v>1037.88</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>950.61</v>
+        <v>1037.88</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>950.61</v>
+        <v>1037.88</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>950.61</v>
+        <v>1037.88</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>950.61</v>
+        <v>1037.88</v>
       </c>
     </row>
     <row r="42">
@@ -3679,34 +3679,34 @@
         <v>4.406555</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>13.82</v>
+        <v>16.42</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>290.51</v>
+        <v>335.18</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>892.15</v>
+        <v>983.39</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>892.15</v>
+        <v>983.39</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>892.15</v>
+        <v>983.39</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>892.15</v>
+        <v>983.39</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>892.15</v>
+        <v>983.39</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>892.15</v>
+        <v>983.39</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>892.15</v>
+        <v>983.39</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>892.15</v>
+        <v>983.39</v>
       </c>
     </row>
     <row r="43">
@@ -3714,34 +3714,34 @@
         <v>5.495365</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>15.43</v>
+        <v>18.33</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>324.44</v>
+        <v>374.33</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>832.42</v>
+        <v>926.12</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>832.42</v>
+        <v>926.12</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>832.42</v>
+        <v>926.12</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>832.42</v>
+        <v>926.12</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>832.42</v>
+        <v>926.12</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>832.42</v>
+        <v>926.12</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>832.42</v>
+        <v>926.12</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>832.42</v>
+        <v>926.12</v>
       </c>
     </row>
     <row r="44">
@@ -3749,34 +3749,34 @@
         <v>6.853207</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v>17.23</v>
+        <v>20.48</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>362.33</v>
+        <v>418.05</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>772.41</v>
+        <v>867</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>772.41</v>
+        <v>867</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>772.41</v>
+        <v>867</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>772.41</v>
+        <v>867</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>772.41</v>
+        <v>867</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>772.41</v>
+        <v>867</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>772.41</v>
+        <v>867</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>772.41</v>
+        <v>867</v>
       </c>
     </row>
     <row r="45">
@@ -3784,34 +3784,34 @@
         <v>8.546557999999999</v>
       </c>
       <c r="B45" s="3" t="n">
-        <v>19.25</v>
+        <v>22.87</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>404.64</v>
+        <v>466.87</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>713.09</v>
+        <v>807.03</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>713.09</v>
+        <v>807.03</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>713.09</v>
+        <v>807.03</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>713.09</v>
+        <v>807.03</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>713.09</v>
+        <v>807.03</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>713.09</v>
+        <v>807.03</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>713.09</v>
+        <v>807.03</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>713.09</v>
+        <v>807.03</v>
       </c>
     </row>
     <row r="46">
@@ -3819,34 +3819,34 @@
         <v>10.658316</v>
       </c>
       <c r="B46" s="3" t="n">
-        <v>21.49</v>
+        <v>25.54</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>451.88</v>
+        <v>521.38</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>655.28</v>
+        <v>747.2</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>655.28</v>
+        <v>747.2</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>655.28</v>
+        <v>747.2</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>655.28</v>
+        <v>747.2</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>655.28</v>
+        <v>747.2</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>655.28</v>
+        <v>747.2</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>655.28</v>
+        <v>747.2</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>655.28</v>
+        <v>747.2</v>
       </c>
     </row>
     <row r="47">
@@ -3854,34 +3854,34 @@
         <v>13.291865</v>
       </c>
       <c r="B47" s="3" t="n">
-        <v>24</v>
+        <v>28.52</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>504.64</v>
+        <v>582.26</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>599.6900000000001</v>
+        <v>688.42</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>599.6900000000001</v>
+        <v>688.42</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>599.6900000000001</v>
+        <v>688.42</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>599.6900000000001</v>
+        <v>688.42</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>599.6900000000001</v>
+        <v>688.42</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>599.6900000000001</v>
+        <v>688.42</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>599.6900000000001</v>
+        <v>688.42</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>599.6900000000001</v>
+        <v>688.42</v>
       </c>
     </row>
     <row r="48">
@@ -3889,34 +3889,34 @@
         <v>16.576135</v>
       </c>
       <c r="B48" s="3" t="n">
-        <v>26.81</v>
+        <v>31.85</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>546.85</v>
+        <v>631.48</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>546.85</v>
+        <v>631.48</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>546.85</v>
+        <v>631.48</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>546.85</v>
+        <v>631.48</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>546.85</v>
+        <v>631.48</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>546.85</v>
+        <v>631.48</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>546.85</v>
+        <v>631.48</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>546.85</v>
+        <v>631.48</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>546.85</v>
+        <v>631.48</v>
       </c>
     </row>
     <row r="49">
@@ -3924,34 +3924,34 @@
         <v>20.671911</v>
       </c>
       <c r="B49" s="3" t="n">
-        <v>29.93</v>
+        <v>35.57</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>497.11</v>
+        <v>576.99</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>497.11</v>
+        <v>576.99</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>497.11</v>
+        <v>576.99</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>497.11</v>
+        <v>576.99</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>497.11</v>
+        <v>576.99</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>497.11</v>
+        <v>576.99</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>497.11</v>
+        <v>576.99</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>497.11</v>
+        <v>576.99</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>497.11</v>
+        <v>576.99</v>
       </c>
     </row>
     <row r="50">
@@ -3959,34 +3959,34 @@
         <v>25.779706</v>
       </c>
       <c r="B50" s="3" t="n">
-        <v>33.43</v>
+        <v>39.72</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>450.7</v>
+        <v>525.42</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>450.7</v>
+        <v>525.42</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>450.7</v>
+        <v>525.42</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>450.7</v>
+        <v>525.42</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>450.7</v>
+        <v>525.42</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>450.7</v>
+        <v>525.42</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>450.7</v>
+        <v>525.42</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>450.7</v>
+        <v>525.42</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>450.7</v>
+        <v>525.42</v>
       </c>
     </row>
     <row r="51">
@@ -3994,34 +3994,34 @@
         <v>32.14958</v>
       </c>
       <c r="B51" s="3" t="n">
-        <v>37.33</v>
+        <v>44.36</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>407.72</v>
+        <v>477.08</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>407.72</v>
+        <v>477.08</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>407.72</v>
+        <v>477.08</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>407.72</v>
+        <v>477.08</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>407.72</v>
+        <v>477.08</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>407.72</v>
+        <v>477.08</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>407.72</v>
+        <v>477.08</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>407.72</v>
+        <v>477.08</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>407.72</v>
+        <v>477.08</v>
       </c>
     </row>
     <row r="52">
@@ -4029,34 +4029,34 @@
         <v>40.093379</v>
       </c>
       <c r="B52" s="3" t="n">
-        <v>41.69</v>
+        <v>49.54</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>368.15</v>
+        <v>432.11</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>368.15</v>
+        <v>432.11</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>368.15</v>
+        <v>432.11</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>368.15</v>
+        <v>432.11</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>368.15</v>
+        <v>432.11</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>368.15</v>
+        <v>432.11</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>368.15</v>
+        <v>432.11</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>368.15</v>
+        <v>432.11</v>
       </c>
       <c r="K52" s="3" t="n">
-        <v>368.15</v>
+        <v>432.11</v>
       </c>
     </row>
     <row r="53">
@@ -4064,34 +4064,34 @@
         <v>50</v>
       </c>
       <c r="B53" s="3" t="n">
-        <v>46.56</v>
+        <v>55.32</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>331.9</v>
+        <v>390.57</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>331.9</v>
+        <v>390.57</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>331.9</v>
+        <v>390.57</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>331.9</v>
+        <v>390.57</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>331.9</v>
+        <v>390.57</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>331.9</v>
+        <v>390.57</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>331.9</v>
+        <v>390.57</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>331.9</v>
+        <v>390.57</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>331.9</v>
+        <v>390.57</v>
       </c>
     </row>
   </sheetData>
@@ -4105,7 +4105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4166,52 +4166,39 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>nearfield_shot</t>
+          <t>quantization</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>449.22</v>
+        <v>37.53</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>449.22</v>
+        <v>37.53</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>quantization</t>
+          <t>read_noise</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>37.53</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>37.53</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>read_noise</t>
+          <t>signal_shot</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>signal_shot</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>74</v>
-      </c>
-      <c r="C9" s="3" t="n">
         <v>1414.21</v>
       </c>
     </row>
@@ -4308,7 +4295,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>6.4 [—]</t>
+          <t>7.6 [—]</t>
         </is>
       </c>
     </row>
